--- a/result/CCND2_LUAD_Tables.xlsx
+++ b/result/CCND2_LUAD_Tables.xlsx
@@ -1677,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,21 +1710,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>ageG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.012</v>
+        <v>1.456</v>
       </c>
       <c r="C2" t="n">
-        <v>0.992</v>
+        <v>1.003</v>
       </c>
       <c r="D2" t="n">
-        <v>1.032</v>
+        <v>2.114</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.048</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="C3" t="n">
         <v>0.992</v>
@@ -1745,196 +1745,70 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>0.874</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>1.487</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.248</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.772</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.060</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>CCND2group_Low</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.164</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0.801</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.691</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>0.426</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.994</v>
+        <v>1.255</v>
       </c>
       <c r="C6" t="n">
-        <v>0.984</v>
+        <v>0.857</v>
       </c>
       <c r="D6" t="n">
-        <v>1.004</v>
+        <v>1.836</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.228</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.998</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.166</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CCND2group_Low</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.219</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.789</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.312</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>gender_MALE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.852</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.279</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pathologic_stage_2.0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.075</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.299</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.315</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.805</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.744</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.512</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.166</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.918</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.017</t>
+          <t>0.243</t>
         </is>
       </c>
     </row>
